--- a/coronavirus_response_forms/007_dental_clinic_covid_19_triage_form--coronavirus_response_forms.xlsx
+++ b/coronavirus_response_forms/007_dental_clinic_covid_19_triage_form--coronavirus_response_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -753,7 +753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>sore_throat</t>
+          <t>difficulty_breathing</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sore Throat</t>
+          <t>Difficulty Breathing</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>difficulty_breathing</t>
+          <t>headache</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Difficulty Breathing</t>
+          <t>Headache</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>headache</t>
+          <t>fatigue</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Headache</t>
+          <t>Fatigue</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>fatigue</t>
+          <t>muscle_or_joint_aches</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fatigue</t>
+          <t>Muscle or Joint Aches</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>muscle_or_joint_aches</t>
+          <t>diarrhea</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Muscle or Joint Aches</t>
+          <t>Diarrhea</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>diarrhea</t>
+          <t>nausea_or_vomiting</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Diarrhea</t>
+          <t>Nausea or Vomiting</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nausea_or_vomiting</t>
+          <t>confusion_or_disorientation</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nausea or Vomiting</t>
+          <t>Confusion or Disorientation</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>confusion_or_disorientation</t>
+          <t>shortness_of_breath</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Confusion or Disorientation</t>
+          <t>Shortness of breath</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>shortness_of_breath</t>
+          <t>chest_pain_or_pressure</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Shortness of breath</t>
+          <t>Chest Pain or Pressure</t>
         </is>
       </c>
     </row>
@@ -1007,29 +1007,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>chest_pain_or_pressure</t>
+          <t>loss_of_smell_or_taste</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chest Pain or Pressure</t>
+          <t>Loss of Smell or Taste</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>symptoms_choices</t>
+          <t>travel_history_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>loss_of_smell_or_taste</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Loss of Smell or Taste</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1041,29 +1041,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>travel_history_choices</t>
+          <t>exposure_history_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1075,29 +1075,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>exposure_history_choices</t>
+          <t>contact_history_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1109,29 +1109,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>contact_history_choices</t>
+          <t>symptoms_duration_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>less_than_24_hours</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Less than 24 hours</t>
         </is>
       </c>
     </row>
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>less_than_24_hours</t>
+          <t>24_to_48_hours</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Less than 24 hours</t>
+          <t>24 to 48 hours</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>24_to_48_hours</t>
+          <t>48_to_72_hours</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>24 to 48 hours</t>
+          <t>48 to 72 hours</t>
         </is>
       </c>
     </row>
@@ -1177,27 +1177,10 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>48_to_72_hours</t>
+          <t>more_than_72_hours</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
-        <is>
-          <t>48 to 72 hours</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>symptoms_duration_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>more_than_72_hours</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
         <is>
           <t>More than 72 hours</t>
         </is>
